--- a/poker/resources/sample/ScratchCards.xlsx
+++ b/poker/resources/sample/ScratchCards.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ScratchCards" sheetId="1" r:id="rId1"/>
@@ -155,79 +160,79 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_14900</t>
+    <t>1990000_188888</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_23800</t>
+    <t>1990000_288888</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_35600</t>
+    <t>1990000_388888</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_41600</t>
+    <t>1990000_488888</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_53500</t>
+    <t>1990000_588888</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_68300</t>
+    <t>1990000_688888</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_89100</t>
+    <t>1990000_888888</t>
   </si>
   <si>
     <t>礼包1</t>
   </si>
   <si>
+    <t>1980000_20</t>
+  </si>
+  <si>
     <t>1022502_2</t>
   </si>
   <si>
-    <t>1_google199|2_ios199</t>
-  </si>
-  <si>
     <t>礼包2</t>
   </si>
   <si>
+    <t>1980000_200</t>
+  </si>
+  <si>
     <t>1022502_20</t>
   </si>
   <si>
-    <t>1_google1999|2_ios1999</t>
-  </si>
-  <si>
     <t>礼包3</t>
   </si>
   <si>
+    <t>1980000_500</t>
+  </si>
+  <si>
     <t>1022502_50</t>
   </si>
   <si>
-    <t>1_google4999|2_ios4999</t>
-  </si>
-  <si>
     <t>礼包4</t>
   </si>
   <si>
+    <t>1980000_1000</t>
+  </si>
+  <si>
     <t>1022502_100</t>
-  </si>
-  <si>
-    <t>1_google9999|2_ios9999</t>
   </si>
 </sst>
 </file>
@@ -422,7 +427,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,175 +442,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799951170384838"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,7 +753,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -778,16 +777,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -796,24 +795,36 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -823,66 +834,57 @@
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -894,19 +896,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1251,153 +1247,153 @@
   <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="12.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="9.25" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9.625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="12.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="30.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9" style="3"/>
+    <col min="11" max="11" width="9.25" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:11">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5">
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6">
         <v>1500</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:11">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6">
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" s="2" customFormat="1" spans="1:11">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -1410,7 +1406,7 @@
       <c r="D7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="s">
         <v>23</v>
@@ -1419,7 +1415,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" s="2" customFormat="1" spans="1:11">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -1432,7 +1428,7 @@
       <c r="D8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="s">
         <v>25</v>
@@ -1440,9 +1436,9 @@
       <c r="H8" s="7">
         <v>1000</v>
       </c>
-      <c r="K8"/>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:11">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -1455,7 +1451,7 @@
       <c r="D9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
         <v>27</v>
@@ -1463,9 +1459,9 @@
       <c r="H9" s="7">
         <v>1000</v>
       </c>
-      <c r="K9"/>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:11">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -1478,7 +1474,7 @@
       <c r="D10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
         <v>29</v>
@@ -1486,9 +1482,9 @@
       <c r="H10" s="7">
         <v>1000</v>
       </c>
-      <c r="K10"/>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:11">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -1501,7 +1497,7 @@
       <c r="D11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7" t="s">
         <v>31</v>
@@ -1509,9 +1505,9 @@
       <c r="H11" s="7">
         <v>1000</v>
       </c>
-      <c r="K11"/>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:11">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -1524,7 +1520,7 @@
       <c r="D12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7" t="s">
         <v>33</v>
@@ -1532,9 +1528,9 @@
       <c r="H12" s="7">
         <v>1000</v>
       </c>
-      <c r="K12"/>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:11">
       <c r="A13" s="7">
         <v>9</v>
       </c>
@@ -1547,7 +1543,7 @@
       <c r="D13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7" t="s">
         <v>35</v>
@@ -1555,109 +1551,101 @@
       <c r="H13" s="7">
         <v>1000</v>
       </c>
-      <c r="K13"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="9">
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:11">
+      <c r="A14" s="7">
         <v>101</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7">
         <v>2</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9">
-        <v>1.99</v>
-      </c>
-      <c r="G14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K14"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="9">
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:11">
+      <c r="A15" s="7">
         <v>102</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7">
         <v>2</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9">
-        <v>19.99</v>
-      </c>
-      <c r="G15" s="9" t="s">
+      <c r="E15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K15"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="9">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:11">
+      <c r="A16" s="7">
         <v>103</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9">
-        <v>49.99</v>
-      </c>
-      <c r="G16" s="9" t="s">
+      <c r="E16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K16"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="9">
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:11">
+      <c r="A17" s="7">
         <v>104</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9">
-        <v>99.99</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9" t="s">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K17"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="K18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="K19"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:11">
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:11">
+      <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11">
       <c r="K20"/>

--- a/poker/resources/sample/ScratchCards.xlsx
+++ b/poker/resources/sample/ScratchCards.xlsx
@@ -60,36 +60,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
-注：1 =  google渠道ID；2 = apple 渠道ID
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>序列ID</t>
   </si>
@@ -115,6 +91,9 @@
     <t>中奖权重值</t>
   </si>
   <si>
+    <t>礼包购买次数/天</t>
+  </si>
+  <si>
     <t>渠道商品ID</t>
   </si>
   <si>
@@ -127,9 +106,6 @@
     <t>BigDecimal</t>
   </si>
   <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -151,6 +127,9 @@
     <t>weight</t>
   </si>
   <si>
+    <t>Count</t>
+  </si>
+  <si>
     <t>channelCommodity</t>
   </si>
   <si>
@@ -160,76 +139,64 @@
     <t>档位1</t>
   </si>
   <si>
-    <t>1990000_188888</t>
+    <t>1980000_88</t>
   </si>
   <si>
     <t>档位2</t>
   </si>
   <si>
-    <t>1990000_288888</t>
+    <t>1980000_188</t>
   </si>
   <si>
     <t>档位3</t>
   </si>
   <si>
-    <t>1990000_388888</t>
+    <t>1980000_388</t>
   </si>
   <si>
     <t>档位4</t>
   </si>
   <si>
-    <t>1990000_488888</t>
+    <t>1980000_588</t>
   </si>
   <si>
     <t>档位5</t>
   </si>
   <si>
-    <t>1990000_588888</t>
+    <t>1980000_888</t>
   </si>
   <si>
     <t>档位6</t>
   </si>
   <si>
-    <t>1990000_688888</t>
+    <t>1980000_1288</t>
   </si>
   <si>
     <t>档位7</t>
   </si>
   <si>
-    <t>1990000_888888</t>
+    <t>1980000_1688</t>
   </si>
   <si>
     <t>礼包1</t>
   </si>
   <si>
-    <t>1980000_20</t>
-  </si>
-  <si>
     <t>1022502_2</t>
   </si>
   <si>
     <t>礼包2</t>
   </si>
   <si>
-    <t>1980000_200</t>
-  </si>
-  <si>
     <t>1022502_20</t>
   </si>
   <si>
     <t>礼包3</t>
   </si>
   <si>
-    <t>1980000_500</t>
-  </si>
-  <si>
     <t>1022502_50</t>
   </si>
   <si>
     <t>礼包4</t>
-  </si>
-  <si>
-    <t>1980000_1000</t>
   </si>
   <si>
     <t>1022502_100</t>
@@ -427,7 +394,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +404,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -753,7 +726,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -777,16 +750,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -795,85 +768,85 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -893,13 +866,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1244,23 +1217,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="3" customWidth="1"/>
     <col min="2" max="3" width="12.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="23.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.875" style="3" customWidth="1"/>
     <col min="7" max="7" width="30.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="25.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9" style="3"/>
-    <col min="11" max="11" width="9.25" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="8" max="9" width="15.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.125" style="3"/>
+    <col min="12" max="12" width="9.25" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1285,38 +1258,44 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="J2" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -1327,23 +1306,26 @@
         <v>15</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="J3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1352,321 +1334,375 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:11">
-      <c r="A5" s="6">
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:12">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:11">
-      <c r="A6" s="6">
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <v>3000</v>
+      </c>
+      <c r="K5" s="7">
+        <f>H5/SUM($H$5:$H$13)</f>
+        <v>0.225563909774436</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:12">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:11">
-      <c r="A7" s="7">
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" ref="K6:K13" si="0">H6/SUM($H$5:$H$13)</f>
+        <v>0.225563909774436</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:12">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7" t="s">
+      <c r="D7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="7">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
-      <c r="A8" s="7">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2500</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18796992481203</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:12">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7" t="s">
+      <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
-      <c r="A9" s="7">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.135338345864662</v>
+      </c>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:12">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
-      <c r="A10" s="7">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1200</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.0902255639097744</v>
+      </c>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:12">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="2">
         <v>6</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:11">
-      <c r="A11" s="7">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <v>800</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.0601503759398496</v>
+      </c>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:12">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="2">
         <v>7</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="2">
         <v>1</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:11">
-      <c r="A12" s="7">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2">
+        <v>500</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="0"/>
+        <v>0.037593984962406</v>
+      </c>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:12">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="2">
         <v>8</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="s">
+      <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:11">
-      <c r="A13" s="7">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="2">
+        <v>300</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="0"/>
+        <v>0.0225563909774436</v>
+      </c>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:12">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="2">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7" t="s">
+      <c r="D13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:11">
-      <c r="A14" s="7">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="2">
+        <v>200</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.0150375939849624</v>
+      </c>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:12">
+      <c r="A14" s="2">
         <v>101</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
         <v>2</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:11">
-      <c r="A15" s="7">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1001</v>
+      </c>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:12">
+      <c r="A15" s="2">
         <v>102</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1003</v>
+      </c>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:12">
+      <c r="A16" s="2">
+        <v>103</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:11">
-      <c r="A16" s="7">
-        <v>103</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7">
+      <c r="F16" s="2">
+        <v>5.99</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2">
         <v>2</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="J16" s="2">
+        <v>1005</v>
+      </c>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:12">
+      <c r="A17" s="2">
+        <v>104</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7" t="s">
+      <c r="F17" s="2">
+        <v>9.99</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:11">
-      <c r="A17" s="7">
-        <v>104</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2">
         <v>2</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:11">
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:11">
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="K20"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="K21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="K22"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="K23"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="K24"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="K25"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="K26"/>
+      <c r="J17" s="2">
+        <v>1007</v>
+      </c>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:12">
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:12">
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="L21"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="L22"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="L23"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="L24"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="L25"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="L26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
